--- a/dataset_t6_grouped/results2/G5/G5_T2372_W0066F0003T0006Z000C1N34_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T2372_W0066F0003T0006Z000C1N34_analysis.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>28.03718979059574</v>
+        <v>9.901900557716276</v>
       </c>
       <c r="D2" t="n">
-        <v>27.75421355512598</v>
+        <v>9.509309975241392</v>
       </c>
       <c r="E2" t="n">
-        <v>19.09510736238077</v>
+        <v>18.48369547623035</v>
       </c>
       <c r="F2" t="n">
-        <v>19.08695626575168</v>
+        <v>18.51959827644362</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>20.49389706054849</v>
+        <v>28.03718979059574</v>
       </c>
       <c r="D3" t="n">
-        <v>20.10153856575468</v>
+        <v>27.75421355512598</v>
       </c>
       <c r="E3" t="n">
-        <v>19.09510736238077</v>
+        <v>18.48369547623035</v>
       </c>
       <c r="F3" t="n">
-        <v>19.08695626575168</v>
+        <v>18.51959827644362</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>11.28000063891215</v>
+        <v>20.49389706054849</v>
       </c>
       <c r="D4" t="n">
-        <v>11.54796546060265</v>
+        <v>20.10153856575468</v>
       </c>
       <c r="E4" t="n">
-        <v>19.09510736238077</v>
+        <v>18.48369547623035</v>
       </c>
       <c r="F4" t="n">
-        <v>19.08695626575168</v>
+        <v>18.51959827644362</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>17.56646340630943</v>
+        <v>11.28000063891215</v>
       </c>
       <c r="D5" t="n">
-        <v>17.72592882690507</v>
+        <v>11.54796546060265</v>
       </c>
       <c r="E5" t="n">
-        <v>19.09510736238077</v>
+        <v>18.48369547623035</v>
       </c>
       <c r="F5" t="n">
-        <v>19.08695626575168</v>
+        <v>18.51959827644362</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>8.867235603373741</v>
+        <v>17.56646340630943</v>
       </c>
       <c r="D6" t="n">
-        <v>9.098497199073911</v>
+        <v>17.72592882690507</v>
       </c>
       <c r="E6" t="n">
-        <v>19.09510736238077</v>
+        <v>18.48369547623035</v>
       </c>
       <c r="F6" t="n">
-        <v>19.08695626575168</v>
+        <v>18.51959827644362</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,23 +640,55 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
+        <v>8.867235603373741</v>
+      </c>
+      <c r="D7" t="n">
+        <v>9.098497199073911</v>
+      </c>
+      <c r="E7" t="n">
+        <v>18.48369547623035</v>
+      </c>
+      <c r="F7" t="n">
+        <v>18.51959827644362</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>T2372</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>G5</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>W0066F0003T0006Z000C1N34.png</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>7</v>
+      </c>
+      <c r="C8" t="n">
         <v>65.68250737939393</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D8" t="n">
         <v>65.84457949820047</v>
       </c>
-      <c r="E7" t="n">
-        <v>19.09510736238077</v>
-      </c>
-      <c r="F7" t="n">
-        <v>19.08695626575168</v>
-      </c>
-      <c r="G7" t="inlineStr">
+      <c r="E8" t="n">
+        <v>18.48369547623035</v>
+      </c>
+      <c r="F8" t="n">
+        <v>18.51959827644362</v>
+      </c>
+      <c r="G8" t="inlineStr">
         <is>
           <t>T2372</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>G5</t>
         </is>

--- a/dataset_t6_grouped/results2/G5/G5_T2372_W0066F0003T0006Z000C1N34_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T2372_W0066F0003T0006Z000C1N34_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>9.901900557716276</v>
+        <v>1.609058840628895</v>
       </c>
       <c r="D2" t="n">
-        <v>9.509309975241392</v>
+        <v>1.545262870976726</v>
       </c>
       <c r="E2" t="n">
-        <v>18.48369547623035</v>
+        <v>3.003600514887432</v>
       </c>
       <c r="F2" t="n">
-        <v>18.51959827644362</v>
+        <v>3.009434719922088</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>28.03718979059574</v>
+        <v>4.556043340971808</v>
       </c>
       <c r="D3" t="n">
-        <v>27.75421355512598</v>
+        <v>4.510059702707971</v>
       </c>
       <c r="E3" t="n">
-        <v>18.48369547623035</v>
+        <v>3.003600514887432</v>
       </c>
       <c r="F3" t="n">
-        <v>18.51959827644362</v>
+        <v>3.009434719922088</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>20.49389706054849</v>
+        <v>3.33025827233913</v>
       </c>
       <c r="D4" t="n">
-        <v>20.10153856575468</v>
+        <v>3.266500016935135</v>
       </c>
       <c r="E4" t="n">
-        <v>18.48369547623035</v>
+        <v>3.003600514887432</v>
       </c>
       <c r="F4" t="n">
-        <v>18.51959827644362</v>
+        <v>3.009434719922088</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>11.28000063891215</v>
+        <v>1.833000103823224</v>
       </c>
       <c r="D5" t="n">
-        <v>11.54796546060265</v>
+        <v>1.876544387347931</v>
       </c>
       <c r="E5" t="n">
-        <v>18.48369547623035</v>
+        <v>3.003600514887432</v>
       </c>
       <c r="F5" t="n">
-        <v>18.51959827644362</v>
+        <v>3.009434719922088</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>17.56646340630943</v>
+        <v>2.854550303525283</v>
       </c>
       <c r="D6" t="n">
-        <v>17.72592882690507</v>
+        <v>2.880463434372075</v>
       </c>
       <c r="E6" t="n">
-        <v>18.48369547623035</v>
+        <v>3.003600514887432</v>
       </c>
       <c r="F6" t="n">
-        <v>18.51959827644362</v>
+        <v>3.009434719922088</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>8.867235603373741</v>
+        <v>1.440925785548233</v>
       </c>
       <c r="D7" t="n">
-        <v>9.098497199073911</v>
+        <v>1.478505794849511</v>
       </c>
       <c r="E7" t="n">
-        <v>18.48369547623035</v>
+        <v>3.003600514887432</v>
       </c>
       <c r="F7" t="n">
-        <v>18.51959827644362</v>
+        <v>3.009434719922088</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>65.68250737939393</v>
+        <v>10.67340744915151</v>
       </c>
       <c r="D8" t="n">
-        <v>65.84457949820047</v>
+        <v>10.69974416845758</v>
       </c>
       <c r="E8" t="n">
-        <v>18.48369547623035</v>
+        <v>3.003600514887432</v>
       </c>
       <c r="F8" t="n">
-        <v>18.51959827644362</v>
+        <v>3.009434719922088</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
